--- a/data/raw/sales/Week 12/Audio_Array/other_channels.xlsx
+++ b/data/raw/sales/Week 12/Audio_Array/other_channels.xlsx
@@ -838,7 +838,7 @@
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>AM-C3A</t>
+          <t>AM-C3a</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
@@ -950,7 +950,7 @@
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>UB-02</t>
+          <t>UB-02 (AM-S1 + AA-21)</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>AI-04</t>
+          <t>AI-04 Red</t>
         </is>
       </c>
       <c r="E5" s="22" t="n">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="C25" s="27" t="inlineStr">
         <is>
-          <t>AH-40-SL</t>
+          <t>AH-40 SL</t>
         </is>
       </c>
       <c r="D25" s="27" t="n">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="C29" s="27" t="inlineStr">
         <is>
-          <t>AM-Mix8</t>
+          <t>AM-Pro8</t>
         </is>
       </c>
       <c r="D29" s="27" t="n">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="C33" s="28" t="inlineStr">
         <is>
-          <t>AA-25 M</t>
+          <t>AA-25M</t>
         </is>
       </c>
       <c r="D33" s="28" t="n">
